--- a/backend/app/agent_artifacts/templates/brand_report_v3.xlsx
+++ b/backend/app/agent_artifacts/templates/brand_report_v3.xlsx
@@ -2,52 +2,141 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-93" yWindow="-93" windowWidth="20186" windowHeight="12800" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="综合概览" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="情感分析" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="日趋势" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="内容与达人" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="地域与话题" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="内容类型与达人" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="地域分布" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="热门帖子TOP" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="洞察与建议" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="舆情洞察" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="方法论" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="TEMPLATE_VERSION">'综合概览'!$A$1000</definedName>
+  </definedNames>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="16">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="001F4E79"/>
+      <color rgb="FF0984E3"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF2D3436"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0984E3"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF00B894"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="11"/>
+      <color rgb="FF00B894"/>
+      <sz val="12"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF636E72"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <sz val="10"/>
+      <color rgb="FFE17055"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0984E3"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF6C5CE7"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFD63031"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFA29BFE"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF636E72"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -59,7 +148,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
+        <fgColor rgb="FF2D3436"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,32 +162,69 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="FFDFE6E9"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="FFDFE6E9"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="FFDFE6E9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="FFDFE6E9"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -458,78 +584,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF0984E3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F1000"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.35"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" style="12" min="1" max="1"/>
+    <col width="39" customWidth="1" style="12" min="2" max="2"/>
+    <col width="20" customWidth="1" style="12" min="3" max="4"/>
+    <col width="13" customWidth="1" style="12" min="5" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="12">
+      <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>核心指标</t>
+          <t>昊来了 品牌社交媒体表现分析报告</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>指标</t>
+          <t>分析周期</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>2026-06-30 至 2026-07-30</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>声量</t>
+          <t>数据来源</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>互动</t>
+          <t>DataTap 聆媒洞察 MCP (小红书 + 抖音)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>发帖</t>
+          <t>搜索方式</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>情感分</t>
+          <t>关键词搜索: "昊来了"</t>
         </is>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="3" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+    </row>
+    <row r="16"/>
+    <row r="17" ht="15.35" customHeight="1" s="12">
+      <c r="A17" s="11" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="22" t="n"/>
+      <c r="D19" s="22" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="22" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="22" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="23" t="n"/>
+    </row>
+    <row r="23"/>
+    <row r="24" ht="15.35" customHeight="1" s="12">
+      <c r="A24" s="11" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="22" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="22" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="22" t="n"/>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>gate-c-v1</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>template_version</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A2:F2"/>
+  <mergeCells count="3">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -538,31 +784,101 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF00B894"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.35"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" style="12" min="1" max="1"/>
+    <col width="13" customWidth="1" style="12" min="2" max="4"/>
+    <col width="17" customWidth="1" style="12" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="17.7" customHeight="1" s="12">
+      <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>情感分析</t>
+          <t>内容情感分布 (按平台)</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="22" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="22" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="22" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="22" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="22" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="22" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="15.35" customHeight="1" s="12">
+      <c r="A11" s="14" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -571,68 +887,226 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFE17055"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.35"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" style="12" min="1" max="1"/>
+    <col width="15" customWidth="1" style="12" min="2" max="3"/>
+    <col width="28" customWidth="1" style="12" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="17.7" customHeight="1" s="12">
+      <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>每日声量与互动趋势</t>
+          <t>每日声量与互动趋势 (2026-06-30 至 2026-07-30)</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>平台</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>声量</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>互动</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>正面</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -641,30 +1115,147 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFFDCB6E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.35"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" style="12" min="1" max="1"/>
+    <col width="13" customWidth="1" style="12" min="2" max="3"/>
+    <col width="17" customWidth="1" style="12" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="17.7" customHeight="1" s="12">
+      <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>内容类型与达人层级</t>
+          <t>内容类型分布</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14" ht="15.35" customHeight="1" s="12">
+      <c r="A14" s="11" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21" ht="15.35" customHeight="1" s="12">
+      <c r="A21" s="11" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n"/>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="22" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -673,24 +1264,151 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF6C5CE7"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.35"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" style="12" min="1" max="1"/>
+    <col width="13" customWidth="1" style="12" min="2" max="3"/>
+    <col width="19" customWidth="1" style="12" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="17.7" customHeight="1" s="12">
+      <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>地域与话题分布</t>
+          <t>发帖用户地域分布 TOP 20</t>
         </is>
       </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="22" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="22" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="22" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="22" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="22" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="22" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="22" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="22" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="22" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="22" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="22" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="22" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="22" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="22" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="22" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="22" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="22" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="22" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="22" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -703,77 +1421,487 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFD63031"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:J3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:L38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.35"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" style="12" min="1" max="1"/>
+    <col width="13" customWidth="1" style="12" min="2" max="2"/>
+    <col width="40" customWidth="1" style="12" min="3" max="3"/>
+    <col width="27" customWidth="1" style="12" min="4" max="4"/>
+    <col width="13" customWidth="1" style="12" min="5" max="12"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="1" ht="17.7" customHeight="1" s="12">
+      <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>排名</t>
+          <t>小红书热门帖子 TOP 15 (品牌相关, 按互动数排序)</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>平台</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>作者</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>发布时间</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>点赞</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>评论</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>转发</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>互动</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>链接</t>
-        </is>
-      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="25.35" customHeight="1" s="12">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21" ht="17.7" customHeight="1" s="12">
+      <c r="A21" s="19" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+    </row>
+    <row r="24" ht="38" customHeight="1" s="12">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="25.35" customHeight="1" s="12">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="25.35" customHeight="1" s="12">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="25.35" customHeight="1" s="12">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="38" customHeight="1" s="12">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="38" customHeight="1" s="12">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="4" t="n"/>
+      <c r="L29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="38" customHeight="1" s="12">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="25.35" customHeight="1" s="12">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+    </row>
+    <row r="32" ht="38" customHeight="1" s="12">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="38" customHeight="1" s="12">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+    </row>
+    <row r="34" ht="38" customHeight="1" s="12">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="25.35" customHeight="1" s="12">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="38" customHeight="1" s="12">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="4" t="n"/>
+      <c r="L36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="25.35" customHeight="1" s="12">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -781,24 +1909,129 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFA29BFE"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.35"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" style="12" min="1" max="2"/>
+    <col width="27" customWidth="1" style="12" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="17.7" customHeight="1" s="12">
+      <c r="A1" s="20" t="inlineStr">
         <is>
-          <t>洞察与建议</t>
+          <t>舆情洞察与内容主题分析</t>
         </is>
       </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n"/>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n"/>
+      <c r="B20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -811,29 +2044,81 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF636E72"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.35"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" style="12" min="1" max="1"/>
+    <col width="70" customWidth="1" style="12" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="1" ht="17.7" customHeight="1" s="12">
+      <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>字段</t>
+          <t>数据说明与方法论</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="38" customHeight="1" s="12">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="63.35" customHeight="1" s="12">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/backend/app/agent_artifacts/templates/brand_report_v3.xlsx
+++ b/backend/app/agent_artifacts/templates/brand_report_v3.xlsx
@@ -15,9 +15,7 @@
     <sheet name="舆情洞察" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="方法论" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <definedNames>
-    <definedName name="TEMPLATE_VERSION">'综合概览'!$A$1000</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -588,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1000"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.35"/>
   <cols>
     <col width="34" customWidth="1" style="12" min="1" max="1"/>
@@ -598,47 +596,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" s="12">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>昊来了 品牌社交媒体表现分析报告</t>
-        </is>
-      </c>
+      <c r="A1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>分析周期</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-30 至 2026-07-30</t>
-        </is>
-      </c>
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>数据来源</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>DataTap 聆媒洞察 MCP (小红书 + 抖音)</t>
-        </is>
-      </c>
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>搜索方式</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>关键词搜索: "昊来了"</t>
-        </is>
-      </c>
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="2" t="n"/>
     </row>
     <row r="5"/>
     <row r="6">
@@ -758,18 +728,6 @@
       <c r="A28" s="4" t="n"/>
       <c r="B28" s="4" t="n"/>
       <c r="C28" s="22" t="n"/>
-    </row>
-    <row r="1000">
-      <c r="A1000" t="inlineStr">
-        <is>
-          <t>gate-c-v1</t>
-        </is>
-      </c>
-      <c r="B1000" t="inlineStr">
-        <is>
-          <t>template_version</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -797,11 +755,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.7" customHeight="1" s="12">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>内容情感分布 (按平台)</t>
-        </is>
-      </c>
+      <c r="A1" s="15" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -900,11 +854,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.7" customHeight="1" s="12">
-      <c r="A1" s="16" t="inlineStr">
-        <is>
-          <t>每日声量与互动趋势 (2026-06-30 至 2026-07-30)</t>
-        </is>
-      </c>
+      <c r="A1" s="16" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -1128,11 +1078,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.7" customHeight="1" s="12">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t>内容类型分布</t>
-        </is>
-      </c>
+      <c r="A1" s="17" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -1277,11 +1223,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.7" customHeight="1" s="12">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>发帖用户地域分布 TOP 20</t>
-        </is>
-      </c>
+      <c r="A1" s="18" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -1436,11 +1378,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.7" customHeight="1" s="12">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>小红书热门帖子 TOP 15 (品牌相关, 按互动数排序)</t>
-        </is>
-      </c>
+      <c r="A1" s="19" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -1921,11 +1859,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.7" customHeight="1" s="12">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>舆情洞察与内容主题分析</t>
-        </is>
-      </c>
+      <c r="A1" s="20" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -2056,11 +1990,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.7" customHeight="1" s="12">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>数据说明与方法论</t>
-        </is>
-      </c>
+      <c r="A1" s="21" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
